--- a/Choix des menus EPS – Terminale (1-2).xlsx
+++ b/Choix des menus EPS – Terminale (1-2).xlsx
@@ -519,15 +519,11 @@
       <c r="A2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>alain.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -548,29 +544,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>10.7</v>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 8.3</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Danse 11.3</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Natation 10.7</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>marie.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -591,29 +589,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>15.2</v>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.1</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.8</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 15.2</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>claire.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>David</t>
@@ -634,29 +634,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>8.1</v>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 17.7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 8.1</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>luc.petit@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Petit</t>
@@ -677,29 +679,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>9.1</v>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Foot 19.5</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 12</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.1</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>jacqueline.martin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Martin</t>
@@ -720,29 +724,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>19.7</v>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Foot 16.8</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 14.4</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.7</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>andré.girardin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Girardin</t>
@@ -763,29 +769,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>14.9</v>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.4</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18.3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 14.9</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>bernard.moreau@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Moreau</t>
@@ -806,29 +814,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>18.4</v>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.8</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.3</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 18.4</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>anne.laurent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Laurent</t>
@@ -849,29 +859,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>16.4</v>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 12.3</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Natation 16.4</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>anne.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>David</t>
@@ -892,29 +904,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>15.7</v>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 12.6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.9</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 15.7</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>andré.caron@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Caron</t>
@@ -935,29 +949,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>8.4</v>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Foot 17.3</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 10.7</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 8.4</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>marc.fournier@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Fournier</t>
@@ -978,29 +994,31 @@
           <t>Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>15.9</v>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Danse 18.5</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.8</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Step 15.9</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>luc.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -1021,29 +1039,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>17</v>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Step 17</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>luc.roux@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Roux</t>
@@ -1064,29 +1084,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>18.3</v>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.9</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 17.1</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 18.3</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>christiane.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -1107,29 +1129,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>13.6</v>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 12.6</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.2</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.6</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>nicole.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -1150,29 +1174,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>12.1</v>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Foot 17</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 17.2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 12.1</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>jean.hubert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Hubert</t>
@@ -1193,29 +1219,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>14</v>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18.5</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Danse 11.2</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>andré.girardin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Girardin</t>
@@ -1236,29 +1264,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>12.5</v>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 14.1</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10.4</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Natation 12.5</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>catherine.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -1279,29 +1309,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M19" s="2" t="n">
-        <v>19.8</v>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 9.3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Danse 12.4</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Natation 19.8</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>philippe.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -1322,29 +1354,31 @@
           <t>Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="M20" s="2" t="n">
-        <v>8.800000000000001</v>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Danse 9</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Natation 13.8</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Step 8.8</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>monique.richard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Richard</t>
@@ -1365,29 +1399,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M21" s="2" t="n">
-        <v>13.1</v>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.2</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.5</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 13.1</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>david.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>André</t>
@@ -1408,29 +1444,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="M22" s="2" t="n">
-        <v>14.2</v>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.8</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.2</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>jacques.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -1451,29 +1489,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M23" s="2" t="n">
-        <v>10.6</v>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.1</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 10.8</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.6</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>marie.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -1494,29 +1534,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M24" s="2" t="n">
-        <v>16</v>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 8.9</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.9</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 16</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>claire.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -1537,29 +1579,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M25" s="2" t="n">
-        <v>9.1</v>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.7</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 12.9</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 9.1</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
         <v>26</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>michel.hubert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>Hubert</t>
@@ -1580,29 +1624,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>15.8</v>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Foot 8.7</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 15.8</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.8</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
         <v>27</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>jacqueline.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -1623,29 +1669,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M27" s="2" t="n">
-        <v>13.4</v>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.3</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 13.4</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>claire.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -1666,29 +1714,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M28" s="2" t="n">
-        <v>14.6</v>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 13.3</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18.3</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 14.6</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
         <v>29</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>anne.garcia@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Garcia</t>
@@ -1709,29 +1759,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M29" s="2" t="n">
-        <v>12.8</v>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.8</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Natation 10.6</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Step 12.8</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>david.lefevre@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Lefevre</t>
@@ -1752,29 +1804,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K30" s="2" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>11.4</v>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.1</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 17.4</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.4</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>isabelle.petit@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>Petit</t>
@@ -1795,29 +1849,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K31" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M31" s="2" t="n">
-        <v>14.5</v>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Foot 19.6</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 15</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 14.5</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>christian.roux@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Roux</t>
@@ -1838,29 +1894,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K32" s="2" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>9</v>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Foot 9.9</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 19.5</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>nicole.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -1881,29 +1939,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K33" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>14.8</v>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 12.8</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 19.3</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 14.8</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>valérie.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>André</t>
@@ -1924,29 +1984,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K34" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>19.2</v>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.3</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Natation 19.2</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>david.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -1967,29 +2029,31 @@
           <t>Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K35" s="2" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M35" s="2" t="n">
-        <v>11.8</v>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.1</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.6</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Step 11.8</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>pierre.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -2010,29 +2074,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K36" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M36" s="2" t="n">
-        <v>19.2</v>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Foot 10.6</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 11.2</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.2</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>anne.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>David</t>
@@ -2053,29 +2119,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K37" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>15.3</v>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.4</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Natation 15.3</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>nicole.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -2096,29 +2164,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K38" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="M38" s="2" t="n">
-        <v>9.4</v>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Foot 19.3</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 9.6</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.4</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>christiane.petit@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>Petit</t>
@@ -2139,29 +2209,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K39" s="2" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="M39" s="2" t="n">
-        <v>15.6</v>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Foot 16.6</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 10.4</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.6</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>pierre.girardin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>Girardin</t>
@@ -2182,29 +2254,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K40" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>8</v>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.1</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Danse 11.3</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Natation 8</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>monique.leroy@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>Leroy</t>
@@ -2225,29 +2299,31 @@
           <t>Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K41" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>8.9</v>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.1</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Natation 8.1</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Step 8.9</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>valérie.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -2268,29 +2344,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K42" s="2" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M42" s="2" t="n">
-        <v>19.2</v>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 8.5</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 12.4</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.2</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>nicole.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -2311,29 +2389,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K43" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M43" s="2" t="n">
-        <v>18.5</v>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 12.2</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.7</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Natation 18.5</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>jacqueline.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -2354,29 +2434,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K44" s="2" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M44" s="2" t="n">
-        <v>10.2</v>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.1</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 12.9</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.2</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>paul.richard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Richard</t>
@@ -2397,29 +2479,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K45" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M45" s="2" t="n">
-        <v>18.5</v>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Danse 17.4</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Natation 9.3</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Step 18.5</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>nathalie.moreau@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>Moreau</t>
@@ -2440,29 +2524,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K46" s="2" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>10.7</v>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17.8</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.5</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 10.7</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>martine.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -2483,29 +2569,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K47" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M47" s="2" t="n">
-        <v>15.7</v>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.6</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.3</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.7</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
         <v>48</v>
       </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>paul.richard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>Richard</t>
@@ -2526,29 +2614,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K48" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M48" s="2" t="n">
-        <v>8.5</v>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.8</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 8.5</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
         <v>49</v>
       </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>valérie.morel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Morel</t>
@@ -2569,29 +2659,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K49" s="2" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>18.8</v>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 19.8</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Danse 9.4</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Natation 18.8</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>jean.roux@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>Roux</t>
@@ -2612,29 +2704,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K50" s="2" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>16.6</v>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 19.1</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.5</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Natation 16.6</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>nicole.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -2655,29 +2749,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K51" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M51" s="2" t="n">
-        <v>9.5</v>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.5</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 16</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 9.5</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
         <v>52</v>
       </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>jacques.michel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -2698,29 +2794,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K52" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>10.3</v>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16.4</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 14.7</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 10.3</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
         <v>53</v>
       </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>david.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -2741,29 +2839,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K53" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M53" s="2" t="n">
-        <v>10.5</v>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 11.6</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 10.5</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
         <v>54</v>
       </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>michel.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>André</t>
@@ -2784,29 +2884,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K54" s="2" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>18.8</v>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 10.6</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.7</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Natation 18.8</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>pierre.gaillard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>Gaillard</t>
@@ -2827,29 +2929,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K55" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="M55" s="2" t="n">
-        <v>11.7</v>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 19.4</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10.8</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.7</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
         <v>56</v>
       </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>claire.bertrand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>Bertrand</t>
@@ -2870,29 +2974,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K56" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>13.5</v>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.3</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 17.2</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 13.5</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
         <v>57</v>
       </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>catherine.michel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -2913,29 +3019,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K57" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>8.1</v>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.9</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.9</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 8.1</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>jacqueline.leroy@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>Leroy</t>
@@ -2956,29 +3064,31 @@
           <t>Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K58" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="M58" s="2" t="n">
-        <v>11</v>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.2</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Natation 8.6</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Step 11</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>nicole.roux@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>Roux</t>
@@ -2999,29 +3109,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K59" s="2" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M59" s="2" t="n">
-        <v>19.4</v>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.9</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.1</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 19.4</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
         <v>60</v>
       </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>anne.hubert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>Hubert</t>
@@ -3042,29 +3154,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K60" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>17</v>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.3</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.4</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>paul.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>David</t>
@@ -3085,29 +3199,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K61" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>11.3</v>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 8.9</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.4</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.3</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
         <v>62</v>
       </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>claire.michel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -3128,29 +3244,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K62" s="2" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>8.800000000000001</v>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16.3</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 16.5</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 8.8</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
         <v>63</v>
       </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>valérie.martin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Martin</t>
@@ -3171,29 +3289,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K63" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="M63" s="2" t="n">
-        <v>18.9</v>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 10.5</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Natation 18.9</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>catherine.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -3214,29 +3334,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K64" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>12.7</v>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Danse 19.3</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.6</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Step 12.7</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>paul.garcia@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Garcia</t>
@@ -3257,29 +3379,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K65" s="2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M65" s="2" t="n">
-        <v>16</v>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.8</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Natation 12.7</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Step 16</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>christiane.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -3300,29 +3424,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K66" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M66" s="2" t="n">
-        <v>14.8</v>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 8.3</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Danse 12.7</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.8</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
         <v>67</v>
       </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>luc.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>David</t>
@@ -3343,29 +3469,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K67" s="2" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>11.9</v>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.2</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 11.1</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 11.9</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
         <v>68</v>
       </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>paul.caron@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>Caron</t>
@@ -3386,29 +3514,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K68" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>18</v>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.4</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.1</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
         <v>69</v>
       </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>nathalie.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -3429,29 +3559,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K69" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>15.8</v>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.8</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Danse 17.4</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Natation 15.8</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>christiane.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -3472,29 +3604,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K70" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M70" s="2" t="n">
-        <v>9.4</v>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.9</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 13.7</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 9.4</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
         <v>71</v>
       </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>bernard.laurent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>Laurent</t>
@@ -3515,29 +3649,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K71" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>17</v>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Natation 15.3</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Step 17</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>philippe.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -3558,29 +3694,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K72" s="2" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>18.9</v>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.1</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 14.9</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.9</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>pierre.fournier@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>Fournier</t>
@@ -3601,29 +3739,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K73" s="2" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>9.199999999999999</v>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 16.3</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.5</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.2</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>nathalie.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -3644,29 +3784,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K74" s="2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>14.1</v>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.1</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Danse 12.4</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.1</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
         <v>75</v>
       </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>sophie.garcia@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>Garcia</t>
@@ -3687,29 +3829,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K75" s="2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>17.9</v>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Danse 19.5</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Natation 15.6</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Step 17.9</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>christiane.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -3730,29 +3874,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K76" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>13.6</v>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 19</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Danse 17.3</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Natation 13.6</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
         <v>77</v>
       </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>andré.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -3773,29 +3919,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K77" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>17</v>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Danse 11.3</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Natation 13.4</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>Step 17</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
         <v>78</v>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>catherine.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -3816,29 +3964,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K78" s="2" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>17.6</v>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.2</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.5</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 17.6</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>monique.dupont@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>Dupont</t>
@@ -3859,29 +4009,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K79" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>10.9</v>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 14.2</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 10.3</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.9</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>françois.bertrand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>Bertrand</t>
@@ -3902,29 +4054,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K80" s="2" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>17.5</v>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 15.8</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.9</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Natation 17.5</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>françois.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -3945,29 +4099,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K81" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>13.7</v>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.7</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 13.7</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>nathalie.leroy@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>Leroy</t>
@@ -3988,29 +4144,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K82" s="2" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>10.8</v>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Foot 13.4</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 11.7</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 10.8</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>marc.petit@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>Petit</t>
@@ -4031,29 +4189,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K83" s="2" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M83" s="2" t="n">
-        <v>15.1</v>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 16.9</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.3</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.1</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
         <v>84</v>
       </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>isabelle.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -4074,29 +4234,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K84" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M84" s="2" t="n">
-        <v>16.5</v>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Foot 12.3</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 11.6</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16.5</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>monique.moreau@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>Moreau</t>
@@ -4117,29 +4279,31 @@
           <t>Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K85" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="M85" s="2" t="n">
-        <v>18.4</v>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.4</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Natation 9.5</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>Step 18.4</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>catherine.bertrand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>Bertrand</t>
@@ -4160,29 +4324,31 @@
           <t>Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K86" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="M86" s="2" t="n">
-        <v>8.6</v>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Danse 13.3</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Natation 10.2</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>Step 8.6</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>catherine.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -4203,29 +4369,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K87" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M87" s="2" t="n">
-        <v>9.800000000000001</v>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 14.9</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 16.2</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.8</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>sophie.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -4246,29 +4414,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K88" s="2" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="M88" s="2" t="n">
-        <v>17.5</v>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17.2</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.3</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 17.5</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
         <v>89</v>
       </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>isabelle.fournier@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>Fournier</t>
@@ -4289,29 +4459,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K89" s="2" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>15.5</v>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.9</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.7</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.5</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>paul.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>André</t>
@@ -4332,29 +4504,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K90" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M90" s="2" t="n">
-        <v>14.6</v>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 9</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10.9</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.6</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>françois.morel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>Morel</t>
@@ -4375,29 +4549,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K91" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>11.5</v>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 13.6</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 8.4</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.5</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>paul.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -4418,29 +4594,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K92" s="2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>17.6</v>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Foot 17.5</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 15.1</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17.6</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>alain.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -4461,29 +4639,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K93" s="2" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M93" s="2" t="n">
-        <v>8.9</v>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.9</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 17.9</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 8.9</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>michel.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -4504,29 +4684,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K94" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="M94" s="2" t="n">
-        <v>12.8</v>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Foot 13.6</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 11.6</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 12.8</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>christiane.martin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>Martin</t>
@@ -4547,29 +4729,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K95" s="2" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>15.2</v>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.7</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 16.8</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.2</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>bernard.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>André</t>
@@ -4590,29 +4774,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K96" s="2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>17.2</v>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17.9</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 14.9</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 17.2</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>paul.richard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>Richard</t>
@@ -4633,29 +4819,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K97" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M97" s="2" t="n">
-        <v>17.8</v>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Foot 20</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 13.2</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 17.8</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
         <v>98</v>
       </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>jacques.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -4676,29 +4864,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K98" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M98" s="2" t="n">
-        <v>12</v>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 18.3</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 12</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>andré.caron@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>Caron</t>
@@ -4719,29 +4909,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K99" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M99" s="2" t="n">
-        <v>11.8</v>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Foot 14.6</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 13.5</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.8</t>
+        </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>nicole.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -4762,29 +4954,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K100" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="M100" s="2" t="n">
-        <v>14.2</v>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.5</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 8.7</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 14.2</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
         <v>101</v>
       </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>bernard.martin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>Martin</t>
@@ -4805,29 +4999,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K101" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M101" s="2" t="n">
-        <v>19.1</v>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.4</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 14.6</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.1</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>alain.morel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>Morel</t>
@@ -4848,29 +5044,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K102" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M102" s="2" t="n">
-        <v>11.7</v>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 17.6</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 16.5</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.7</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
         <v>103</v>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>andré.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -4891,29 +5089,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K103" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L103" s="2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M103" s="2" t="n">
-        <v>18</v>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.5</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9.4</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 18</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
         <v>104</v>
       </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>valérie.gaillard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>Gaillard</t>
@@ -4934,29 +5134,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K104" s="2" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="M104" s="2" t="n">
-        <v>13.5</v>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Foot 13.8</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 13.7</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.5</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
         <v>105</v>
       </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>martine.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -4977,29 +5179,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K105" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="M105" s="2" t="n">
-        <v>13</v>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.3</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Danse 17.5</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>Natation 13</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
         <v>106</v>
       </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>sylvie.moreau@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>Moreau</t>
@@ -5020,29 +5224,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K106" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M106" s="2" t="n">
-        <v>15.9</v>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 15.9</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
         <v>107</v>
       </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>nathalie.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -5063,29 +5269,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K107" s="2" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M107" s="2" t="n">
-        <v>13.5</v>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 14.6</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.5</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>Natation 13.5</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>philippe.michel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -5106,29 +5314,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K108" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>8.5</v>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10.8</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Natation 17.3</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>Step 8.5</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
         <v>109</v>
       </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>catherine.martin@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>Martin</t>
@@ -5149,29 +5359,31 @@
           <t>Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K109" s="2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>12</v>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Danse 9.5</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Natation 19.6</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>Step 12</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
         <v>110</v>
       </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>jean.hubert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>Hubert</t>
@@ -5192,29 +5404,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K110" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="L110" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>19.6</v>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Foot 9.7</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 18.5</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.6</t>
+        </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
         <v>111</v>
       </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>christiane.leroy@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>Leroy</t>
@@ -5235,29 +5449,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K111" s="2" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>11.9</v>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 12.8</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 11.9</t>
+        </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
         <v>112</v>
       </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>martine.vincent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>Vincent</t>
@@ -5278,29 +5494,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K112" s="2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>15.6</v>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 8.4</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Danse 8.8</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>Natation 15.6</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
         <v>113</v>
       </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>valérie.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -5321,29 +5539,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K113" s="2" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>9.199999999999999</v>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Foot 17.1</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 16.4</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.2</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
         <v>114</v>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>jacques.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -5364,29 +5584,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K114" s="2" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M114" s="2" t="n">
-        <v>13.2</v>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Foot 8.7</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 12.3</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.2</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
         <v>115</v>
       </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>anne.richard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>Richard</t>
@@ -5407,29 +5629,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>15.4</v>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Foot 8.9</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 18.5</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.4</t>
+        </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
         <v>116</v>
       </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>claire.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>David</t>
@@ -5450,29 +5674,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K116" s="2" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>16</v>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.7</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.5</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
         <v>117</v>
       </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>pierre.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>David</t>
@@ -5493,29 +5719,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K117" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>11.6</v>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 19.3</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.9</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 11.6</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
         <v>118</v>
       </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>marc.michel@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>Michel</t>
@@ -5536,29 +5764,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K118" s="2" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>12.6</v>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.2</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9.3</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 12.6</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
         <v>119</v>
       </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>jean.gaillard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>Gaillard</t>
@@ -5579,29 +5809,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K119" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>14.8</v>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Danse 15.9</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.3</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>Step 14.8</t>
+        </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>christiane.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -5622,29 +5854,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K120" s="2" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>15.5</v>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Foot 12.2</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 15.6</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.5</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
         <v>121</v>
       </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>isabelle.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -5665,29 +5899,31 @@
           <t>Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K121" s="2" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>16.8</v>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Foot 13.3</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Musculation 15</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16.8</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
         <v>122</v>
       </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>anne.petit@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>Petit</t>
@@ -5708,29 +5944,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K122" s="2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>19.7</v>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 9.6</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.5</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>Natation 19.7</t>
+        </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
         <v>123</v>
       </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>andré.bertrand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>Bertrand</t>
@@ -5751,29 +5989,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K123" s="2" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>18.4</v>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.6</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.5</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.4</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
         <v>124</v>
       </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>bernard.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -5794,29 +6034,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K124" s="2" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>19.8</v>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18.3</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.7</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>Natation 19.8</t>
+        </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
         <v>125</v>
       </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>jean.lefevre@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>Lefevre</t>
@@ -5837,29 +6079,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>16.1</v>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 14.4</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 13.5</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 16.1</t>
+        </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>sophie.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>André</t>
@@ -5880,29 +6124,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K126" s="2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>18.6</v>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 10.8</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 8.3</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.6</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>alain.bernard@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>Bernard</t>
@@ -5923,29 +6169,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>16.4</v>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.6</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 13.6</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 16.4</t>
+        </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>marie.moreau@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>Moreau</t>
@@ -5966,29 +6214,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K128" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>10.8</v>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 20</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9.4</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 10.8</t>
+        </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>nathalie.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>André</t>
@@ -6009,29 +6259,31 @@
           <t>Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K129" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="M129" s="2" t="n">
-        <v>14.5</v>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Danse 19.4</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Natation 16.4</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>Step 14.5</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>andré.bertrand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>Bertrand</t>
@@ -6052,29 +6304,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K130" s="2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="M130" s="2" t="n">
-        <v>11.4</v>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.4</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 19.3</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 11.4</t>
+        </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>claire.laurent@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>Laurent</t>
@@ -6095,29 +6349,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu B : Escalade / Volley-ball / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K131" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M131" s="2" t="n">
-        <v>14.5</v>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 9.2</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Danse 16.2</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>Natation 14.5</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>marc.thomas@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>Thomas</t>
@@ -6138,29 +6394,31 @@
           <t>Menu C : Danse / Natation / Step;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K132" s="2" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M132" s="2" t="n">
-        <v>9.1</v>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Danse 19.4</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Natation 17.9</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>Step 9.1</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>claire.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -6181,29 +6439,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K133" s="2" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M133" s="2" t="n">
-        <v>18</v>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 17.4</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Danse 10.5</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>Natation 18</t>
+        </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
         <v>134</v>
       </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>andré.durand@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>Durand</t>
@@ -6224,29 +6484,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K134" s="2" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="L134" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="M134" s="2" t="n">
-        <v>18.8</v>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 11.9</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 9.8</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 18.8</t>
+        </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
         <v>135</v>
       </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>monique.lefevre@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>Lefevre</t>
@@ -6267,29 +6529,31 @@
           <t>Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;</t>
         </is>
       </c>
-      <c r="K135" s="2" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M135" s="2" t="n">
-        <v>18.4</v>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Danse 17.6</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Natation 9.3</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>Step 18.4</t>
+        </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
         <v>136</v>
       </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>philippe.simon@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>Simon</t>
@@ -6310,29 +6574,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;Menu D : Volley-ball / Danse / Natation;</t>
         </is>
       </c>
-      <c r="K136" s="2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M136" s="2" t="n">
-        <v>9.5</v>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 8.2</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 11.2</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 9.5</t>
+        </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>catherine.david@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>David</t>
@@ -6353,29 +6619,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K137" s="2" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M137" s="2" t="n">
-        <v>9.300000000000001</v>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 17.3</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Danse 14.2</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Natation 9.3</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>sylvie.renaud@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>Renaud</t>
@@ -6396,29 +6664,31 @@
           <t>Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K138" s="2" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M138" s="2" t="n">
-        <v>11.6</v>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 18.9</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Danse 15.9</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Natation 11.6</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>valérie.andré@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>André</t>
@@ -6439,29 +6709,31 @@
           <t>Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;Menu A : Demi-fond / Escalade / Badminton;</t>
         </is>
       </c>
-      <c r="K139" s="2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M139" s="2" t="n">
-        <v>13.3</v>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9.3</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Volley-ball 16.5</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 13.3</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>pierre.robert@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>Robert</t>
@@ -6482,29 +6754,31 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;Menu D : Volley-ball / Danse / Natation;Menu C : Danse / Natation / Step;</t>
         </is>
       </c>
-      <c r="K140" s="2" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M140" s="2" t="n">
-        <v>14.6</v>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 11.3</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 15.6</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 14.6</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>michel.roux@eps-vauban.fr</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>Roux</t>
@@ -6525,14 +6799,20 @@
           <t>Menu A : Demi-fond / Escalade / Badminton;Menu C : Danse / Natation / Step;Menu D : Volley-ball / Danse / Natation;Menu B : Escalade / Volley-ball / Demi-fond;Menu E : Foot / Musculation / Demi-fond;</t>
         </is>
       </c>
-      <c r="K141" s="2" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="M141" s="2" t="n">
-        <v>16.4</v>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Demi-fond 15.3</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>Escalade 9.2</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Badminton 16.4</t>
+        </is>
       </c>
     </row>
   </sheetData>
